--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI68"/>
+  <dimension ref="A1:BI72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46139.50694444445</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.50694444445</v>
       </c>
     </row>
     <row r="21">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46139.55555555555</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46139.5625</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="29">
@@ -6067,27 +6067,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.55555555555</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.5625</v>
       </c>
     </row>
     <row r="31">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46139.60416666666</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -9022,27 +9022,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -9219,27 +9219,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.60416666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46139.64583333334</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="47">
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="51">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="53">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46139.77083333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="56">
@@ -11386,27 +11386,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="57">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.77083333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="60">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,27 +12568,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="63">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,145 +13799,933 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI68" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI69" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI68" s="3" t="n">
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI71" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="3" t="n">
         <v>46139.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI72"/>
+  <dimension ref="A1:BI78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="18">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46139.50694444445</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="24">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.50694444445</v>
       </c>
     </row>
     <row r="26">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46139.55555555555</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46139.5625</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="31">
@@ -6461,27 +6461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.55555555555</v>
       </c>
     </row>
     <row r="35">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.5625</v>
       </c>
     </row>
     <row r="36">
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.5625</v>
       </c>
     </row>
     <row r="37">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46139.60416666666</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -9416,27 +9416,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46139.64583333334</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -10204,27 +10204,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.14</v>
+        <v>3.32</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="R51" t="n">
-        <v>3.93</v>
+        <v>2.19</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.60416666666</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="54">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="57">
@@ -11583,27 +11583,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="58">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46139.77083333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="60">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="64">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.77083333334</v>
       </c>
     </row>
     <row r="65">
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="66">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="67">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="68">
@@ -13750,27 +13750,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="69">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14587,145 +14587,1327 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH72" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI72" s="3" t="n">
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI73" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI74" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI75" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI76" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI77" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI78" s="3" t="n">
         <v>46139.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI78"/>
+  <dimension ref="A1:BI82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="23">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46139.50694444445</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.50694444445</v>
       </c>
     </row>
     <row r="27">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46139.55555555555</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46139.5625</v>
+        <v>46139.55555555555</v>
       </c>
     </row>
     <row r="36">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.63</v>
+        <v>5.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.18</v>
+        <v>3.99</v>
       </c>
       <c r="R37" t="n">
-        <v>6.16</v>
+        <v>1.7</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.5625</v>
       </c>
     </row>
     <row r="38">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46139.60416666666</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.60416666666</v>
       </c>
     </row>
     <row r="54">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46139.64583333334</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="56">
@@ -11386,27 +11386,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="57">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="58">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="60">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="61">
@@ -12371,27 +12371,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="62">
@@ -12568,27 +12568,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="63">
@@ -12765,27 +12765,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="64">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46139.77083333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="65">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="66">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="67">
@@ -13553,27 +13553,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="68">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.77083333334</v>
       </c>
     </row>
     <row r="69">
@@ -13947,27 +13947,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="70">
@@ -14144,27 +14144,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="73">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15720,27 +15720,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,6 +15908,794 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI79" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI80" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI81" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI82" s="3" t="n">
         <v>46139.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3610,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>6.16</v>
+        <v>2.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R21" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R40" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>4.18</v>
       </c>
       <c r="R42" t="n">
-        <v>2.35</v>
+        <v>6.16</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="R47" t="n">
-        <v>6.16</v>
+        <v>7.5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R61" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="R47" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>5.56</v>
+        <v>2.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3610,10 +3610,10 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R44" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R48" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>7.5</v>
+        <v>5.56</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R61" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3413,10 +3413,10 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.35</v>
+        <v>5.56</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>7.6</v>
+        <v>2.75</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.33</v>
+        <v>4.18</v>
       </c>
       <c r="R45" t="n">
-        <v>7.5</v>
+        <v>6.16</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>5.56</v>
+        <v>7.5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R15" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3413,10 +3413,10 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R17" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3807,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R20" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="R30" t="n">
-        <v>2.77</v>
+        <v>4.21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="R42" t="n">
-        <v>5.56</v>
+        <v>2.83</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R44" t="n">
-        <v>2.75</v>
+        <v>4.39</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>2.35</v>
+        <v>5.56</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI82"/>
+  <dimension ref="A1:BI83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46139.46875</v>
+        <v>46139.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46139.46875</v>
+        <v>46139.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3807,10 +3807,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46139.46875</v>
+        <v>46139.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.9</v>
+        <v>3.78</v>
       </c>
       <c r="R20" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46139.47916666666</v>
+        <v>46139.46875</v>
       </c>
     </row>
     <row r="23">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46139.5</v>
+        <v>46139.47916666666</v>
       </c>
     </row>
     <row r="26">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46139.50694444445</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="27">
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="28">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.5</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46139.54166666666</v>
+        <v>46139.50694444445</v>
       </c>
     </row>
     <row r="30">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46139.55555555555</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46139.5625</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.99</v>
+        <v>3.86</v>
       </c>
       <c r="R37" t="n">
-        <v>1.7</v>
+        <v>4.21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46139.5625</v>
+        <v>46139.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.54861111111</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>7.6</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.5625</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46139.58333333334</v>
+        <v>46139.5625</v>
       </c>
     </row>
     <row r="41">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.18</v>
+        <v>3.52</v>
       </c>
       <c r="R43" t="n">
-        <v>6.16</v>
+        <v>4.39</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="R44" t="n">
-        <v>4.39</v>
+        <v>7.5</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="R52" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46139.60416666666</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="54">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -11189,27 +11189,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -11386,27 +11386,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46139.625</v>
+        <v>46139.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46139.64583333334</v>
+        <v>46139.60416666666</v>
       </c>
     </row>
     <row r="58">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46139.64583333334</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="59">
@@ -11977,12 +11977,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46139.64583333334</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="60">
@@ -12174,27 +12174,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.625</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.56</v>
+        <v>3.77</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R61" t="n">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46139.65625</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="63">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46139.66666666666</v>
+        <v>46139.64583333334</v>
       </c>
     </row>
     <row r="64">
@@ -12962,27 +12962,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="65">
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.65625</v>
       </c>
     </row>
     <row r="66">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="67">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46139.67708333334</v>
+        <v>46139.66666666666</v>
       </c>
     </row>
     <row r="68">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46139.77083333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="69">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46139.79166666666</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.67708333334</v>
       </c>
     </row>
     <row r="72">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46139.83333333334</v>
+        <v>46139.77083333334</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.79166666666</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46139.875</v>
+        <v>46139.83333333334</v>
       </c>
     </row>
     <row r="77">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16508,27 +16508,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,6 +16696,203 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
+        <v>46139.875</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI83" s="3" t="n">
         <v>46139.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>4.21</v>
+        <v>2.77</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.7</v>
+        <v>5.56</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R22" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="R37" t="n">
-        <v>2.77</v>
+        <v>4.21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="R47" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>6.16</v>
+        <v>2.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R50" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R51" t="n">
-        <v>2.75</v>
+        <v>4.39</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.6</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>2.78</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="R53" t="n">
-        <v>5.56</v>
+        <v>2.83</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.18</v>
+        <v>3.52</v>
       </c>
       <c r="R41" t="n">
-        <v>6.16</v>
+        <v>4.39</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.6</v>
+        <v>4.18</v>
       </c>
       <c r="R47" t="n">
-        <v>7.6</v>
+        <v>6.16</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>7.5</v>
+        <v>5.56</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>4.39</v>
+        <v>2.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="R52" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
-        <v>2.78</v>
+        <v>7.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="R46" t="n">
-        <v>7.5</v>
+        <v>2.78</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>6.16</v>
+        <v>2.75</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R48" t="n">
-        <v>2.75</v>
+        <v>4.39</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R51" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>5.56</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="R37" t="n">
-        <v>2.77</v>
+        <v>4.21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>7.5</v>
+        <v>5.56</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>4.39</v>
+        <v>2.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="R52" t="n">
-        <v>5.56</v>
+        <v>6.16</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R56" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.63</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>2.35</v>
+        <v>7.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>4.18</v>
       </c>
       <c r="R48" t="n">
-        <v>2.75</v>
+        <v>6.16</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>4.39</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R50" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.6</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>7.6</v>
+        <v>2.78</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R22" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.35</v>
+        <v>5.56</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>4.39</v>
+        <v>2.75</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.18</v>
+        <v>5.6</v>
       </c>
       <c r="R48" t="n">
-        <v>6.16</v>
+        <v>7.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="R50" t="n">
-        <v>7.6</v>
+        <v>2.83</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R53" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R41" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>4.39</v>
+        <v>2.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>7.6</v>
+        <v>5.56</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R54" t="n">
-        <v>2.35</v>
+        <v>4.39</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R22" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="R48" t="n">
-        <v>5.56</v>
+        <v>4.39</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>4.33</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>7.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="R50" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>6.16</v>
+        <v>5.56</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>4.21</v>
+        <v>2.77</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R42" t="n">
-        <v>2.7</v>
+        <v>7.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.18</v>
+        <v>3.52</v>
       </c>
       <c r="R44" t="n">
-        <v>6.16</v>
+        <v>4.39</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
         <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>4.39</v>
+        <v>2.78</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.6</v>
+        <v>4.18</v>
       </c>
       <c r="R50" t="n">
-        <v>7.6</v>
+        <v>6.16</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R51" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R22" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R46" t="n">
-        <v>2.7</v>
+        <v>4.39</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.18</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>6.16</v>
+        <v>2.78</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R42" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="R45" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>6.16</v>
+        <v>2.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="R54" t="n">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="R55" t="n">
-        <v>5.56</v>
+        <v>6.16</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>7.6</v>
+        <v>2.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.52</v>
+        <v>4.33</v>
       </c>
       <c r="R47" t="n">
-        <v>4.39</v>
+        <v>7.5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>2.78</v>
+        <v>4.25</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="R53" t="n">
-        <v>7.5</v>
+        <v>2.78</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.18</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
-        <v>6.16</v>
+        <v>4.39</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.66</v>
+        <v>3.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>4.21</v>
+        <v>1.97</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.6</v>
+        <v>3.52</v>
       </c>
       <c r="R43" t="n">
-        <v>7.6</v>
+        <v>4.39</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R50" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="R51" t="n">
-        <v>4.25</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.42</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.78</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.52</v>
+        <v>4.18</v>
       </c>
       <c r="R55" t="n">
-        <v>4.39</v>
+        <v>6.16</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>5.56</v>
+        <v>2.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R25" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.66</v>
+        <v>3.61</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>4.21</v>
+        <v>1.97</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="R43" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.42</v>
+        <v>1.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="R46" t="n">
-        <v>2.78</v>
+        <v>4.39</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.33</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>7.5</v>
+        <v>2.78</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R49" t="n">
-        <v>5.56</v>
+        <v>7.6</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>2.35</v>
+        <v>5.56</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.6</v>
+        <v>4.18</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>6.16</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>2.35</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="R56" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>2.87</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.87</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.61</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.97</v>
+        <v>4.54</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>4.25</v>
+        <v>2.03</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R44" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R45" t="n">
-        <v>2.75</v>
+        <v>4.39</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,55 +9469,55 @@
         </is>
       </c>
       <c r="P46" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R46" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q46" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.33</v>
+        <v>5.6</v>
       </c>
       <c r="R47" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>5.56</v>
+        <v>2.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>6.16</v>
+        <v>2.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R54" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.21</v>
+        <v>1.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.74</v>
+        <v>4.18</v>
       </c>
       <c r="R56" t="n">
-        <v>2.83</v>
+        <v>6.16</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="R20" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>3.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.16</v>
+        <v>2.87</v>
       </c>
       <c r="R25" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.61</v>
+        <v>1.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.97</v>
+        <v>4.54</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="R42" t="n">
-        <v>5.56</v>
+        <v>2.83</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>4.39</v>
+        <v>5.56</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.92</v>
+        <v>3.35</v>
       </c>
       <c r="R46" t="n">
-        <v>5.09</v>
+        <v>4.25</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="R48" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R51" t="n">
-        <v>2.7</v>
+        <v>4.39</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>2.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.7</v>
+        <v>1.61</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R54" t="n">
-        <v>2.35</v>
+        <v>5.09</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P82" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI83"/>
+  <dimension ref="A1:BI82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46139.45138888889</v>
+        <v>46139.375</v>
       </c>
     </row>
     <row r="7">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46139.45833333334</v>
+        <v>46139.45138888889</v>
       </c>
     </row>
     <row r="8">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R20" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4398,10 +4398,10 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
         <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>4.54</v>
+        <v>2.77</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="R35" t="n">
-        <v>2.77</v>
+        <v>4.21</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="R41" t="n">
-        <v>7.5</v>
+        <v>5.09</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.83</v>
+        <v>5.56</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R43" t="n">
-        <v>2.35</v>
+        <v>4.39</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.59</v>
+        <v>3.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>5.56</v>
+        <v>2.03</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>4.25</v>
+        <v>2.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.18</v>
+        <v>3.6</v>
       </c>
       <c r="R49" t="n">
-        <v>6.16</v>
+        <v>2.35</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.52</v>
+        <v>4.18</v>
       </c>
       <c r="R51" t="n">
-        <v>4.39</v>
+        <v>6.16</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.03</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="R55" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -16696,203 +16696,6 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46139.875</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46139</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI83" s="3" t="n">
         <v>46139.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.14</v>
+        <v>3.78</v>
       </c>
       <c r="R20" t="n">
-        <v>4.04</v>
+        <v>2.37</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4398,10 +4398,10 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>2.87</v>
       </c>
       <c r="R24" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.87</v>
+        <v>3.16</v>
       </c>
       <c r="R25" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R39" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.59</v>
+        <v>3.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>5.56</v>
+        <v>2.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>4.39</v>
+        <v>5.56</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>2.03</v>
+        <v>2.78</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
         <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="R48" t="n">
-        <v>7.6</v>
+        <v>2.83</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R50" t="n">
         <v>2.35</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R50" t="n">
-        <v>2.75</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.18</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>6.16</v>
+        <v>4.25</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.42</v>
+        <v>1.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>5.6</v>
       </c>
       <c r="R52" t="n">
-        <v>2.78</v>
+        <v>7.6</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>7.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="R55" t="n">
-        <v>2.83</v>
+        <v>5.09</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R23" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5538,19 +5538,19 @@
         <v>3.45</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.61</v>
+        <v>1.71</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.97</v>
+        <v>4.54</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="R43" t="n">
-        <v>5.56</v>
+        <v>6.16</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.18</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>6.16</v>
+        <v>2.75</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>2.75</v>
+        <v>5.56</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>4.39</v>
+        <v>2.03</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="R51" t="n">
-        <v>4.25</v>
+        <v>7.6</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.6</v>
+        <v>3.74</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R56" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="R19" t="n">
-        <v>2.37</v>
+        <v>4.04</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="R21" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.87</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R24" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,28 +5726,28 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -5765,40 +5765,40 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5843,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5932,19 +5932,19 @@
         <v>3.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="Q34" t="n">
         <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>2.77</v>
+        <v>4.54</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>3.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>4.21</v>
+        <v>1.97</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.55</v>
+        <v>5.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="R40" t="n">
-        <v>4.24</v>
+        <v>1.7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R42" t="n">
         <v>2.7</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.35</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="R43" t="n">
-        <v>6.16</v>
+        <v>5.09</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R44" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R45" t="n">
-        <v>2.7</v>
+        <v>4.39</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="Q46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U46" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W46" t="n">
         <v>4</v>
       </c>
-      <c r="R46" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="R47" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.78</v>
+        <v>2.03</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.99</v>
+        <v>3.02</v>
       </c>
       <c r="Q75" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R75" t="n">
-        <v>4.21</v>
+        <v>2.32</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>2.32</v>
+        <v>4.21</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G81" t="n">

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1007,13 +1007,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="V3" t="n">
         <v>1.3</v>
@@ -1037,25 +1037,25 @@
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AD3" t="n">
         <v>3.82</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
         <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.09</v>
@@ -1070,7 +1070,7 @@
         <v>1.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4201,10 +4201,10 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI21" t="n">
         <v>4.2</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BD25" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,28 +5726,28 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -5765,40 +5765,40 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5843,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,28 +5923,28 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
         <v>3.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.66</v>
+        <v>3.61</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>4.21</v>
+        <v>1.97</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7114,19 +7114,19 @@
         <v>4.54</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.86</v>
       </c>
       <c r="R36" t="n">
-        <v>1.97</v>
+        <v>4.21</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA39" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R39" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,19 +8401,19 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R41" t="n">
-        <v>2.35</v>
+        <v>4.25</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q42" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R42" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU42" t="n">
         <v>3.4</v>
       </c>
-      <c r="R42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.92</v>
+        <v>5.6</v>
       </c>
       <c r="R43" t="n">
-        <v>5.09</v>
+        <v>7.6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.9</v>
+        <v>2.74</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>4.25</v>
+        <v>2.35</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.78</v>
+        <v>2.42</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>4.39</v>
+        <v>2.78</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>7.6</v>
+        <v>2.75</v>
       </c>
       <c r="S46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>2.83</v>
+        <v>5.56</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="R50" t="n">
-        <v>6.16</v>
+        <v>5.09</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="R52" t="n">
-        <v>2.78</v>
+        <v>7.5</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="R53" t="n">
-        <v>5.56</v>
+        <v>2.83</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.33</v>
+        <v>5.34</v>
       </c>
       <c r="R56" t="n">
         <v>7.5</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.2</v>
+        <v>3.96</v>
       </c>
       <c r="R59" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,79 +12424,79 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR61" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW61" t="n">
         <v>0</v>
@@ -12532,25 +12532,25 @@
         <v>0</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13221,124 +13221,124 @@
         <v>2.67</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG65" t="n">
         <v>0</v>
@@ -13606,133 +13606,133 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR67" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS67" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU67" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV67" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD67" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE67" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF67" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14445,10 +14445,10 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,17 +16360,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.88</v>
+        <v>4.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="X9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS9" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AT9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.37</v>
       </c>
-      <c r="Z9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AY9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R13" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R21" t="n">
         <v>3.6</v>
       </c>
-      <c r="R21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="S21" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U21" t="n">
-        <v>2.88</v>
+        <v>4.09</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W21" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="X21" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC21" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4.85</v>
+        <v>5.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q23" t="n">
         <v>3.1</v>
       </c>
       <c r="R23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="AF23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL23" t="n">
         <v>1.95</v>
       </c>
-      <c r="U23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH23" t="n">
+      <c r="AM23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
         <v>1.17</v>
       </c>
-      <c r="AI23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="AQ23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.22</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.63</v>
+        <v>2.19</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
-        <v>3.48</v>
+        <v>3.97</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="U24" t="n">
-        <v>3.56</v>
+        <v>2.64</v>
       </c>
       <c r="V24" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="X24" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
         <v>2.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AG24" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK24" t="n">
         <v>2.02</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BE24" t="n">
         <v>1.44</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2.87</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.78</v>
+        <v>3.48</v>
       </c>
       <c r="T25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK25" t="n">
         <v>2.02</v>
       </c>
-      <c r="U25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AL25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.37</v>
       </c>
-      <c r="Z25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.19</v>
+        <v>2.56</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,28 +5726,28 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -5765,40 +5765,40 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5843,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,28 +5923,28 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
         <v>3.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI28" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.61</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U33" t="n">
         <v>3.25</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.68</v>
+        <v>1.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.7</v>
+        <v>4.24</v>
       </c>
       <c r="S39" t="n">
-        <v>4.7</v>
+        <v>1.95</v>
       </c>
       <c r="T39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN39" t="n">
         <v>2.3</v>
       </c>
-      <c r="U39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BA40" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q40" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R40" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W40" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM40" t="n">
+      <c r="BB40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BF40" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>4.25</v>
+        <v>2.03</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.52</v>
+        <v>5.6</v>
       </c>
       <c r="R42" t="n">
-        <v>4.39</v>
+        <v>7.6</v>
       </c>
       <c r="S42" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT42" t="n">
         <v>2.3</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH42" t="n">
+      <c r="AU42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>1.29</v>
       </c>
-      <c r="AI42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.42</v>
-      </c>
       <c r="BA42" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.6</v>
+        <v>3.92</v>
       </c>
       <c r="R43" t="n">
-        <v>7.6</v>
+        <v>5.09</v>
       </c>
       <c r="S43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.74</v>
+        <v>1.9</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R44" t="n">
         <v>2.7</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R44" t="n">
-        <v>2.35</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="R47" t="n">
-        <v>5.56</v>
+        <v>6.16</v>
       </c>
       <c r="S47" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="T47" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="U47" t="n">
-        <v>4.6</v>
+        <v>5.87</v>
       </c>
       <c r="V47" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W47" t="n">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="X47" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.19</v>
+        <v>3.32</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI47" t="n">
-        <v>6</v>
+        <v>6.41</v>
       </c>
       <c r="AJ47" t="n">
         <v>1.1</v>
       </c>
       <c r="AK47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL47" t="n">
         <v>1.8</v>
       </c>
-      <c r="AL47" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AM47" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="BA47" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R49" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.61</v>
+        <v>2.42</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.92</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>5.09</v>
+        <v>2.78</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>5.34</v>
       </c>
       <c r="R51" t="n">
-        <v>2.7</v>
+        <v>7.5</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W52" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q52" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.83</v>
+        <v>4.25</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>6.16</v>
+        <v>5.56</v>
       </c>
       <c r="S54" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="T54" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
-        <v>5.87</v>
+        <v>4.6</v>
       </c>
       <c r="V54" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W54" t="n">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="X54" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB54" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AE54" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AI54" t="n">
-        <v>6.41</v>
+        <v>6</v>
       </c>
       <c r="AJ54" t="n">
         <v>1.1</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AM54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY54" t="n">
         <v>1.28</v>
       </c>
-      <c r="AN54" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT54" t="n">
+      <c r="AZ54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD54" t="n">
         <v>3.6</v>
       </c>
-      <c r="AU54" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>3.78</v>
-      </c>
       <c r="BE54" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W55" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC55" t="n">
         <v>2.2</v>
       </c>
-      <c r="S55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W55" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD55" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,133 +11439,133 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA56" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,79 +12424,79 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN61" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR61" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
         <v>0</v>
@@ -12532,25 +12532,25 @@
         <v>0</v>
       </c>
       <c r="AZ61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC61" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12702,7 +12702,7 @@
         <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR62" t="n">
         <v>0</v>
@@ -12717,7 +12717,7 @@
         <v>0</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW62" t="n">
         <v>0</v>
@@ -12729,25 +12729,25 @@
         <v>0</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="R70" t="n">
-        <v>6.6</v>
+        <v>3.58</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="R71" t="n">
-        <v>3.58</v>
+        <v>6.6</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,16 +14439,16 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -14591,133 +14591,133 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.77</v>
+        <v>4.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="R72" t="n">
         <v>1.7</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AF72" t="n">
         <v>1.75</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO72" t="n">
         <v>0</v>
       </c>
       <c r="AP72" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU72" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV72" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX72" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY72" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ72" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BA72" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BB72" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC72" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,133 +14985,133 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO74" t="n">
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU74" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW74" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX74" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY74" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB74" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC74" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BD74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF74" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>2.32</v>
+        <v>4.21</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.99</v>
+        <v>3.02</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R76" t="n">
-        <v>4.21</v>
+        <v>2.32</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15769,17 +15769,17 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,17 +15966,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,17 +16163,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R19" t="n">
         <v>3.6</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.63</v>
-      </c>
       <c r="S19" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.38</v>
+        <v>4.09</v>
       </c>
       <c r="V19" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>3.25</v>
+        <v>3.82</v>
       </c>
       <c r="X19" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.45</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>2.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.52</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AN19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC19" t="n">
         <v>1.57</v>
       </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD19" t="n">
-        <v>4.45</v>
+        <v>5.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD21" t="n">
         <v>4.2</v>
       </c>
-      <c r="R21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AE21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.36</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3.97</v>
+        <v>3.48</v>
       </c>
       <c r="T24" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>2.64</v>
+        <v>3.56</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="X24" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
         <v>2.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK24" t="n">
         <v>2.02</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BE24" t="n">
         <v>1.44</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.48</v>
+        <v>3.97</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
-        <v>3.56</v>
+        <v>2.64</v>
       </c>
       <c r="V25" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="X25" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
         <v>2.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
         <v>2.02</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BE25" t="n">
         <v>1.44</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,28 +5726,28 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
         <v>3.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -5765,40 +5765,40 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AI27" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5843,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,28 +5923,28 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="Q33" t="n">
         <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.77</v>
+        <v>4.54</v>
       </c>
       <c r="S33" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="U33" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="X33" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK33" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="Q34" t="n">
         <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>4.54</v>
+        <v>2.77</v>
       </c>
       <c r="S34" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U34" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AF34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7538,40 +7538,40 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,79 +7696,79 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.61</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.97</v>
+        <v>3.45</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7810,19 +7810,19 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="R41" t="n">
-        <v>2.03</v>
+        <v>5.09</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.92</v>
+        <v>3.63</v>
       </c>
       <c r="R43" t="n">
-        <v>5.09</v>
+        <v>2.2</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T44" t="n">
         <v>2.7</v>
       </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="Q45" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU45" t="n">
         <v>3.4</v>
       </c>
-      <c r="R45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="R46" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.18</v>
+        <v>5.34</v>
       </c>
       <c r="R47" t="n">
-        <v>6.16</v>
+        <v>7.5</v>
       </c>
       <c r="S47" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="T47" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="U47" t="n">
-        <v>5.87</v>
+        <v>7.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W47" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="X47" t="n">
-        <v>2.89</v>
+        <v>2.27</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="Z47" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.39</v>
+        <v>4.8</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.02</v>
+        <v>1.56</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>3.32</v>
+        <v>2.45</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>6.41</v>
+        <v>3.92</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.33</v>
+        <v>3.25</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AW47" t="n">
         <v>1.72</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="BA47" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.21</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="R48" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.42</v>
+        <v>1.59</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>2.78</v>
+        <v>5.56</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.34</v>
+        <v>3.35</v>
       </c>
       <c r="R51" t="n">
-        <v>7.5</v>
+        <v>4.25</v>
       </c>
       <c r="S51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,133 +10651,133 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.63</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="S52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>4.33</v>
       </c>
       <c r="R53" t="n">
-        <v>4.25</v>
+        <v>7.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,133 +11045,133 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.59</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R54" t="n">
-        <v>5.56</v>
+        <v>2.7</v>
       </c>
       <c r="S54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO54" t="n">
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BA54" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>4.39</v>
+        <v>2.03</v>
       </c>
       <c r="S55" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="T55" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U55" t="n">
-        <v>4.6</v>
+        <v>2.55</v>
       </c>
       <c r="V55" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.93</v>
+        <v>2.48</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z55" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12030,79 +12030,79 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO59" t="n">
         <v>0</v>
@@ -12144,19 +12144,19 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,79 +12227,79 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO60" t="n">
         <v>0</v>
@@ -12341,19 +12341,19 @@
         <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12702,7 +12702,7 @@
         <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR62" t="n">
         <v>0</v>
@@ -12717,7 +12717,7 @@
         <v>0</v>
       </c>
       <c r="AV62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW62" t="n">
         <v>0</v>
@@ -12729,25 +12729,25 @@
         <v>0</v>
       </c>
       <c r="AZ62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,79 +12818,79 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
@@ -12899,7 +12899,7 @@
         <v>0</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR63" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW63" t="n">
         <v>0</v>
@@ -12926,25 +12926,25 @@
         <v>0</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BB63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC63" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,133 +13015,133 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>3.93</v>
+        <v>2.67</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO64" t="n">
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AS64" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA64" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,133 +13212,133 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.67</v>
+        <v>3.93</v>
       </c>
       <c r="S65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM65" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AN65" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR65" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AU65" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ65" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC65" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,133 +13409,133 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.37</v>
+        <v>3.5</v>
       </c>
       <c r="R66" t="n">
-        <v>5.12</v>
+        <v>4.06</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL66" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR66" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS66" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV66" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD66" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,133 +13606,133 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.5</v>
+        <v>4.37</v>
       </c>
       <c r="R67" t="n">
-        <v>4.06</v>
+        <v>5.12</v>
       </c>
       <c r="S67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS67" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU67" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV67" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD67" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,79 +13803,79 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
@@ -13917,19 +13917,19 @@
         <v>0</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="R70" t="n">
-        <v>3.58</v>
+        <v>6.6</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,16 +14242,16 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,79 +14394,79 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="R71" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE71" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AG71" t="n">
         <v>1.98</v>
       </c>
-      <c r="AF71" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
@@ -14508,19 +14508,19 @@
         <v>0</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
@@ -15003,7 +15003,7 @@
         <v>3.58</v>
       </c>
       <c r="V74" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W74" t="n">
         <v>2.39</v>
@@ -15024,7 +15024,7 @@
         <v>1.04</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AD74" t="n">
         <v>2.63</v>
@@ -15051,7 +15051,7 @@
         <v>2</v>
       </c>
       <c r="AL74" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM74" t="n">
         <v>1.4</v>
@@ -15063,55 +15063,55 @@
         <v>0</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AS74" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU74" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="AV74" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AW74" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AX74" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AY74" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AZ74" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BA74" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BB74" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BC74" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BD74" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BE74" t="n">
         <v>1.44</v>
       </c>
       <c r="BF74" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,79 +15182,79 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>4.21</v>
+        <v>2.3</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
@@ -15296,19 +15296,19 @@
         <v>0</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD75" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF75" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,79 +15379,79 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>2.32</v>
+        <v>4.21</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
@@ -15493,19 +15493,19 @@
         <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC76" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="BD76" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="BE76" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BF76" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,133 +15970,133 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.07</v>
+        <v>1.62</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.45</v>
+        <v>3.68</v>
       </c>
       <c r="R79" t="n">
-        <v>3.31</v>
+        <v>5.55</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN79" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR79" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS79" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU79" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW79" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BA79" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB79" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC79" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE79" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF79" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,79 +16167,79 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="R80" t="n">
-        <v>5.55</v>
+        <v>3.31</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
@@ -16281,19 +16281,19 @@
         <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>

--- a/jogos_2026-04-27.xlsx
+++ b/jogos_2026-04-27.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="R8" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>5.92</v>
+        <v>3.6</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG8" t="n">
         <v>3.4</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.35</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.96</v>
+        <v>1.59</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="BA8" t="n">
         <v>2.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="S10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="S13" t="n">
         <v>4.34</v>
@@ -3004,7 +3004,7 @@
         <v>1.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
         <v>1.48</v>
@@ -3016,7 +3016,7 @@
         <v>2.48</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG13" t="n">
         <v>4.6</v>
@@ -3031,10 +3031,10 @@
         <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM13" t="n">
         <v>1.36</v>
@@ -3046,28 +3046,28 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AT13" t="n">
         <v>3.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AX13" t="n">
         <v>1.37</v>
@@ -3076,22 +3076,22 @@
         <v>1.22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="BB13" t="n">
         <v>1.33</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BD13" t="n">
         <v>2.91</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BF13" t="n">
         <v>1.06</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="S22" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="T22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
         <v>2.02</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="AL22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX22" t="n">
         <v>1.4</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AY22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BC22" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.8</v>
-      </c>
       <c r="T23" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
         <v>2.8</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="X23" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>4.26</v>
+        <v>3.34</v>
       </c>
       <c r="AH23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
         <v>1.17</v>
       </c>
-      <c r="AI23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AQ23" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.7</v>
+        <v>3.86</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.73</v>
+        <v>2.72</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -5371,40 +5371,40 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5449,13 +5449,13 @@
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.54</v>
+        <v>3.75</v>
       </c>
       <c r="S29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>4.7</v>
+        <v>4.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AI29" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL29" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH29" t="n">
+      <c r="AM29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB29" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI29" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
       <c r="BC29" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q39" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R39" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.75</v>
       </c>
-      <c r="S39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="AI39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE39" t="n">
         <v>2.15</v>
       </c>
-      <c r="U39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
+      <c r="BF39" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.47</v>
+        <v>4.6</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S40" t="n">
         <v>4.6</v>
       </c>
-      <c r="R40" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW40" t="n">
         <v>1.88</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W40" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>5.5</v>
+        <v>3.82</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="R41" t="n">
-        <v>2.03</v>
+        <v>7</v>
       </c>
       <c r="S41" t="n">
-        <v>3.55</v>
+        <v>1.91</v>
       </c>
       <c r="T41" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X41" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC41" t="n">
         <v>1.95</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
         <v>1.78</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U42" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AF42" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>2.68</v>
+        <v>5.56</v>
       </c>
       <c r="S43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD43" t="n">
         <v>3.2</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AE43" t="n">
-        <v>2.21</v>
+        <v>1.96</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI43" t="n">
-        <v>7.4</v>
+        <v>6.15</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AU43" t="n">
-        <v>4.95</v>
+        <v>2.95</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.34</v>
+        <v>2.2</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.41</v>
+        <v>1.75</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="R44" t="n">
-        <v>4.6</v>
+        <v>2.83</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="S45" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="U45" t="n">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="V45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.22</v>
       </c>
-      <c r="W45" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AD45" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AM45" t="n">
         <v>1.25</v>
       </c>
       <c r="AN45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC45" t="n">
         <v>1.91</v>
       </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BD45" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BE45" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="S46" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC46" t="n">
         <v>2.15</v>
       </c>
-      <c r="U46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BD46" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>4.24</v>
+        <v>4.07</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.96</v>
+        <v>3.05</v>
       </c>
       <c r="R48" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="S48" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="T48" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="U48" t="n">
-        <v>5.55</v>
+        <v>3.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W48" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="X48" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN48" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z48" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AR48" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.59</v>
+        <v>1.79</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.96</v>
+        <v>4.95</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.72</v>
+        <v>2.41</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.29</v>
+        <v>2.13</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.78</v>
+        <v>3.28</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.15</v>
+        <v>3.25</v>
       </c>
       <c r="R49" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="T49" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="U49" t="n">
-        <v>8</v>
+        <v>5.08</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="W49" t="n">
-        <v>4.1</v>
+        <v>2.77</v>
       </c>
       <c r="X49" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AB49" t="n">
         <v>1.01</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AD49" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AI49" t="n">
-        <v>3.25</v>
+        <v>6.7</v>
       </c>
       <c r="AJ49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB49" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK49" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC49" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R50" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T50" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q50" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.87</v>
-      </c>
       <c r="U50" t="n">
-        <v>3.26</v>
+        <v>8</v>
       </c>
       <c r="V50" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="W50" t="n">
-        <v>2.59</v>
+        <v>3.9</v>
       </c>
       <c r="X50" t="n">
-        <v>3.18</v>
+        <v>2.07</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="Z50" t="n">
-        <v>8.1</v>
+        <v>4.45</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.62</v>
+        <v>5.85</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF50" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR50" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AH50" t="n">
+      <c r="AS50" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="BB50" t="n">
         <v>1.17</v>
       </c>
-      <c r="AI50" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP50" t="n">
+      <c r="BC50" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BF50" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>1.09</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,133 +10454,133 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.4</v>
+        <v>2.79</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="R51" t="n">
-        <v>7</v>
+        <v>2.49</v>
       </c>
       <c r="S51" t="n">
-        <v>1.8</v>
+        <v>3.45</v>
       </c>
       <c r="T51" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="U51" t="n">
-        <v>6.5</v>
+        <v>3.29</v>
       </c>
       <c r="V51" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W51" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="X51" t="n">
-        <v>2.59</v>
+        <v>3.18</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AD51" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.76</v>
+        <v>3.96</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.25</v>
+        <v>7.7</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL51" t="n">
         <v>1.83</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.6</v>
+        <v>3.74</v>
       </c>
       <c r="AU51" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.18</v>
+        <v>2.19</v>
       </c>
       <c r="BA51" t="n">
-        <v>6.14</v>
+        <v>2.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="BC51" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.3</v>
+        <v>3.12</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,79 +10651,79 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="Q52" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R52" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U52" t="n">
         <v>5.55</v>
       </c>
-      <c r="R52" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U52" t="n">
-        <v>7</v>
-      </c>
       <c r="V52" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="W52" t="n">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="X52" t="n">
-        <v>2.27</v>
+        <v>3.05</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.05</v>
+        <v>7.1</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AD52" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.4</v>
+        <v>3.38</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AI52" t="n">
-        <v>3.92</v>
+        <v>6.15</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AN52" t="n">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -10732,13 +10732,13 @@
         <v>1.28</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AT52" t="n">
         <v>3.42</v>
@@ -10747,13 +10747,13 @@
         <v>3.08</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AY52" t="n">
         <v>1.23</v>
@@ -10762,22 +10762,22 @@
         <v>1.26</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.7</v>
+        <v>5.49</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="BD52" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="BF52" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,118 +10848,118 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.51</v>
+        <v>1.34</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.44</v>
+        <v>5.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.55</v>
+        <v>7.5</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="T53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U53" t="n">
+        <v>7</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG53" t="n">
         <v>2.4</v>
       </c>
-      <c r="U53" t="n">
-        <v>3</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W53" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X53" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AH53" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI53" t="n">
-        <v>4.51</v>
+        <v>3.92</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL53" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AM53" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AQ53" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>1.26</v>
       </c>
-      <c r="AR53" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BA53" t="n">
-        <v>2.37</v>
+        <v>4.7</v>
       </c>
       <c r="BB53" t="n">
         <v>1.18</v>
@@ -10971,7 +10971,7 @@
         <v>4.4</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
    